--- a/reports/二级子公司C_利润表_2025-09.xlsx
+++ b/reports/二级子公司C_利润表_2025-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>92435482</v>
+        <v>94928348</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>89759697</v>
+        <v>90151973</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>779398891</v>
+        <v>780386676</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>421286</v>
+        <v>418086</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3646778</v>
+        <v>3640725</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>367748</v>
+        <v>366560</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3190001</v>
+        <v>3186245</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>314424</v>
+        <v>314967</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2733263</v>
+        <v>2731930</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>292821</v>
+        <v>294695</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2550046</v>
+        <v>2550784</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>156636</v>
+        <v>158196</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1365630</v>
+        <v>1367018</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>125244</v>
+        <v>126718</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1092257</v>
+        <v>1093964</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>90757323</v>
+        <v>93249126</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>88081538</v>
+        <v>88472751</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>83852929</v>
+        <v>84294225</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>728354806</v>
+        <v>729388737</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1260954</v>
+        <v>1261507</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>10929109</v>
+        <v>10937905</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>842631</v>
+        <v>838891</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>7288938</v>
+        <v>7289291</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3165609</v>
+        <v>3138645</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>27343635</v>
+        <v>27324082</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>422481</v>
+        <v>417793</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>3646847</v>
+        <v>3641914</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>316833</v>
+        <v>313116</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2735533</v>
+        <v>2730737</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>527471</v>
+        <v>522032</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4559139</v>
+        <v>4550733</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>631743</v>
+        <v>627271</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5469993</v>
+        <v>5461182</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2625892</v>
+        <v>2619101</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>22784661</v>
+        <v>22759714</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49893</v>
+        <v>50012</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>449947</v>
+        <v>449908</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1263365</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>10932509</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>843897</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7291112</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>62473832</v>
+        <v>67551962</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>55656703</v>
+        <v>56137898</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>54398499</v>
+        <v>54873837</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>473328733</v>
+        <v>474158627</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1258204</v>
+        <v>1264061</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>10925772</v>
+        <v>10940521</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2101814</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18229038</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>670893</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5831130</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>418375</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3643024</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>501274</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4370117</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>375733</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3276808</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>250606</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2184346</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>209141</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1820430</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>945002</v>
+        <v>943175</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8202086</v>
+        <v>8193809</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>733193</v>
+        <v>735418</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6376939</v>
+        <v>6375134</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>627173</v>
+        <v>631870</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5463846</v>
+        <v>5466541</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4697944</v>
+        <v>4747898</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>40965927</v>
+        <v>41014412</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>198809</v>
+        <v>211233</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1798203</v>
+        <v>1823393</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>348201</v>
+        <v>352052</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3146968</v>
+        <v>3153169</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>398633</v>
+        <v>352052</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3597273</v>
+        <v>3153169</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>49945</v>
+        <v>50147</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>449811</v>
+        <v>450311</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>180095</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1620534</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>366776</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3188732</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>119506</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1079469</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>89501</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>809344</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>149100</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1348671</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>522169</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4550725</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>79693</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>719416</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>59903</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>539730</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100090</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>899914</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>70228</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>630205</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>50252</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>450309</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40237</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>360334</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30173</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>270272</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28283491</v>
+        <v>26965873</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32999739</v>
+        <v>30492934</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>210040</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1822735</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>49886</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>449933</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>80436</v>
+        <v>79651</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>720566</v>
+        <v>719610</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28203055</v>
+        <v>27096262</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2815374</v>
+        <v>2783265</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>25224998</v>
+        <v>25174954</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25387681</v>
+        <v>24312997</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25387681</v>
+        <v>24312997</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25387681</v>
+        <v>24312997</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25387681</v>
+        <v>24312997</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25387681</v>
+        <v>24312997</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
